--- a/output/laminas_comunales/comunal_s_fonasa_a_2022_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2022_o_higgins.xlsx
@@ -375,301 +375,301 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="C2">
-        <v>208069</v>
+        <v>93.2413729470382</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Chépica</t>
         </is>
       </c>
       <c r="C3">
-        <v>70476</v>
+        <v>92.83038038991553</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Palmilla</t>
         </is>
       </c>
       <c r="C4">
-        <v>59232</v>
+        <v>92.68712809270279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Chimbarongo</t>
         </is>
       </c>
       <c r="C5">
-        <v>43964</v>
+        <v>92.40650365388019</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Paredones</t>
         </is>
       </c>
       <c r="C6">
-        <v>38297</v>
+        <v>92.28653925477795</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
+          <t>Lolol</t>
         </is>
       </c>
       <c r="C7">
-        <v>36544</v>
+        <v>92.12517634987816</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Machalí</t>
+          <t>Peralillo</t>
         </is>
       </c>
       <c r="C8">
-        <v>33423</v>
+        <v>91.51300054008179</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Graneros</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="C9">
-        <v>32274</v>
+        <v>91.21262547640775</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>Malloa</t>
         </is>
       </c>
       <c r="C10">
-        <v>27982</v>
+        <v>91.08012103670569</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="C11">
-        <v>26713</v>
+        <v>90.97658480868076</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="C12">
-        <v>24534</v>
+        <v>90.47870236054332</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Coltauco</t>
+          <t>La Estrella</t>
         </is>
       </c>
       <c r="C13">
-        <v>21049</v>
+        <v>90.14249007241298</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Coltauco</t>
         </is>
       </c>
       <c r="C14">
-        <v>20304</v>
+        <v>90.10316339197809</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Marchigüe</t>
         </is>
       </c>
       <c r="C15">
-        <v>20211</v>
+        <v>89.86336193199872</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Doñihue</t>
+          <t>Las Cabras</t>
         </is>
       </c>
       <c r="C16">
-        <v>20165</v>
+        <v>89.85804628632938</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Placilla</t>
         </is>
       </c>
       <c r="C17">
-        <v>16992</v>
+        <v>89.79908764437542</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chépica</t>
+          <t>Pumanque</t>
         </is>
       </c>
       <c r="C18">
-        <v>14618</v>
+        <v>89.78964783739069</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="C19">
-        <v>14337</v>
+        <v>89.6693714424125</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Malloa</t>
+          <t>Litueche</t>
         </is>
       </c>
       <c r="C20">
-        <v>13846</v>
+        <v>89.14210583981593</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="C21">
-        <v>13722</v>
+        <v>89.13675337886934</v>
       </c>
     </row>
     <row r="22">
@@ -684,187 +684,187 @@
         </is>
       </c>
       <c r="C22">
-        <v>13297</v>
+        <v>88.08293587705353</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="C23">
-        <v>12503</v>
+        <v>87.96628077912533</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Peralillo</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="C24">
-        <v>11861</v>
+        <v>87.20939458859002</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Palmilla</t>
+          <t>Doñihue</t>
         </is>
       </c>
       <c r="C25">
-        <v>11838</v>
+        <v>87.07198065546872</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Placilla</t>
+          <t>Navidad</t>
         </is>
       </c>
       <c r="C26">
-        <v>9252</v>
+        <v>86.83985851933163</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Marchigüe</t>
+          <t>Coinco</t>
         </is>
       </c>
       <c r="C27">
-        <v>8484</v>
+        <v>86.64545025931164</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Litueche</t>
+          <t>Graneros</t>
         </is>
       </c>
       <c r="C28">
-        <v>8136</v>
+        <v>86.39344701126964</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Coinco</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="C29">
-        <v>7351</v>
+        <v>86.11052207472751</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lolol</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="C30">
-        <v>7183</v>
+        <v>84.74951297530004</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Navidad</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="C31">
-        <v>7120</v>
+        <v>84.56586781105503</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Paredones</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="C32">
-        <v>6712</v>
+        <v>84.00860041658268</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>La Estrella</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="C33">
-        <v>3859</v>
+        <v>79.39080135224853</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>Machalí</t>
         </is>
       </c>
       <c r="C34">
-        <v>3799</v>
+        <v>59.34270800042612</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +920,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
